--- a/data/simulation_schedule.xlsx
+++ b/data/simulation_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legend" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Schedule" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +461,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Period: 2026-07-10 to 2026-09-07</t>
+          <t>Period: 2026-08-30 to 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>See data/training/simulation_report.md for the aggregate numbers behind this schedule.</t>
+          <t>See data/simulation_report.md for the aggregate numbers behind this schedule.</t>
         </is>
       </c>
     </row>
@@ -555,58 +555,50 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
       <c r="C2" s="4" t="inlineStr"/>
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>[heavy] Farmer's carry
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>[heavy] Suitcase carry
 [light] Running
 [light] Toes-to-bar
 [light] Kettlebell swing
-[light] Push-up</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>[heavy] Deadlift
-[light] Air squat
-[hhr] Farmer's carry
-[hhr] Strict pull-up
-[hhr] Strict press</t>
+[light] Ring row</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Front squat
-[hhr] Kettlebell swing
-[light] Rowing (erg)
-[light] Toes-to-bar
-[light] Push-up</t>
+          <t>[heavy] Deadlift
+[light] Push-up
+[light] Air squat
+[hhr] Farmer's carry
+[hhr] Strict pull-up</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Bent-over row
-[hhr] Dumbbell lunge
-[light] Kettlebell swing
-[hhr] Farmer's carry
-[hhr] Bench press</t>
+          <t>[heavy] Strict press
+[hhr] Kettlebell snatch
+[hhr] Front squat
+[light] Rowing (erg)
+[light] Toes-to-bar</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -615,36 +607,36 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Thruster
-[hhr] Strict pull-up
-[hhr] Deadlift
-[light] Double-unders
-[light] Toes-to-bar</t>
+          <t>[heavy] Bent-over row
+[hhr] Handstand push-up
+[light] Devil's press
+[light] Air squat
+[hhr] Dumbbell box step-over</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Strict press
-[light] Air squat
-[light] Kettlebell swing
-[hhr] Farmer's carry
-[hhr] Bent-over row</t>
+          <t>[heavy] Dumbbell lunge
+[light] Kipping pull-up
+[hhr] Dumbbell snatch
+[hhr] Man maker
+[light] Double-unders</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Deadlift
-[hhr] Back squat
+          <t>[heavy] Suitcase carry
+[light] Kettlebell swing
 [light] Push-up
-[light] Burpee
-[light] Toes-to-bar</t>
+[light] Toes-to-bar
+[hhr] Strict pull-up</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
@@ -653,36 +645,36 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Farmer's carry
-[light] Air squat
-[light] Kettlebell swing
-[light] Push-up
-[light] Biking</t>
+          <t>[heavy] Deadlift
+[light] Air squat
+[light] Ring row
+[hhr] Farmer's carry
+[light] Devil's press</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Strict pull-up
-[hhr] Bench press
-[hhr] Deadlift
-[hhr] Front squat
-[light] Toes-to-bar</t>
+          <t>[heavy] Bench press
+[hhr] Kettlebell snatch
+[light] Burpee box jump-over
+[light] Toes-to-bar
+[hhr] Back squat</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Dumbbell lunge
+          <t>[heavy] Bent-over row
 [light] Kettlebell swing
+[light] Air squat
 [light] Push-up
-[hhr] Farmer's carry
-[light] Running</t>
+[hhr] Dumbbell box step-over</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -691,36 +683,36 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Thruster
+          <t>[heavy] Suitcase carry
+[light] Kipping pull-up
+[light] Burpee
 [light] Toes-to-bar
-[hhr] Bent-over row
-[light] Kettlebell swing
-[light] Rowing (erg)</t>
+[hhr] Dumbbell snatch</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Deadlift
-[light] Air squat
-[light] Push-up
-[light] Toes-to-bar
-[hhr] Farmer's carry</t>
+          <t>[heavy] Thruster
+[hhr] Man maker
+[light] Devil's press
+[light] Box jump-over
+[light] Toes-to-bar</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Strict press
-[light] Air squat
-[hhr] Kettlebell swing
-[light] Double-unders
-[hhr] Strict pull-up</t>
+          <t>[heavy] Deadlift
+[light] Air squat
+[light] Ring row
+[light] Push-up
+[hhr] Farmer's carry</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
@@ -729,36 +721,36 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Farmer's carry
+          <t>[heavy] Strict pull-up
 [light] Kettlebell swing
-[hhr] Bench press
-[hhr] Back squat
-[light] Toes-to-bar</t>
+[light] Air squat
+[hhr] Dumbbell thruster
+[light] Biking</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Bent-over row
-[light] Push-up
-[light] Air squat
-[light] Kettlebell swing
-[light] Burpee</t>
+          <t>[heavy] Front squat
+[hhr] Bent-over row
+[light] Toes-to-bar
+[hhr] Kettlebell snatch
+[hhr] Dumbbell box step-over</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Deadlift
-[light] Push-up
-[light] Air squat
-[light] Toes-to-bar
-[light] Biking</t>
+          <t>[heavy] Strict press
+[light] Kipping pull-up
+[light] Devil's press
+[light] Air squat
+[light] Running</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -767,36 +759,36 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Front squat
-[light] Kettlebell swing
-[hhr] Thruster
-[light] Toes-to-bar
-[hhr] Farmer's carry</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>[heavy] Strict press
-[light] Air squat
-[hhr] Deadlift
-[light] Running
-[hhr] Strict pull-up</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>[heavy] Farmer's carry
+          <t>[heavy] Suitcase carry
 [light] Push-up
 [light] Kettlebell swing
 [light] Toes-to-bar
-[light] Air squat</t>
+[light] Ring row</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>[heavy] Dumbbell snatch
+[light] Air squat
+[light] Rowing (erg)
+[hhr] Man maker
+[light] Toes-to-bar</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>[heavy] Strict pull-up
+[light] Devil's press
+[hhr] Farmer's carry
+[light] Air squat
+[light] Double-unders</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
@@ -805,36 +797,36 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Bent-over row
+          <t>[heavy] Dumbbell lunge
+[light] Kipping pull-up
 [light] Push-up
-[light] Rowing (erg)
-[hhr] Dumbbell lunge
-[light] Kettlebell swing</t>
+[light] Kettlebell swing
+[light] Toes-to-bar</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>[heavy] Deadlift
-[hhr] Bench press
-[light] Toes-to-bar
-[light] Air squat
-[light] Double-unders</t>
+[hhr] Bent-over row
+[hhr] Handstand push-up
+[light] Air squat
+[light] Burpee box jump-over</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Farmer's carry
-[light] Push-up
-[light] Kettlebell swing
+          <t>[heavy] Dumbbell box step-over
+[hhr] Kettlebell snatch
+[light] Ring row
 [light] Toes-to-bar
-[light] Air squat</t>
+[light] Burpee</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -843,36 +835,36 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Back squat
-[hhr] Deadlift
-[light] Push-up
-[light] Burpee
-[hhr] Farmer's carry</t>
+          <t>[heavy] Suitcase carry
+[light] Devil's press
+[light] Kipping pull-up
+[light] Air squat
+[light] Toes-to-bar</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Thruster
+          <t>[heavy] Bench press
 [light] Kettlebell swing
-[light] Toes-to-bar
-[hhr] Strict pull-up
-[light] Biking</t>
+[hhr] Man maker
+[light] Box jump-over
+[light] Toes-to-bar</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Strict press
-[light] Air squat
-[light] Kettlebell swing
-[light] Toes-to-bar
-[light] Running</t>
+          <t>[heavy] Strict pull-up
+[light] Push-up
+[hhr] Dumbbell snatch
+[light] Air squat
+[hhr] Farmer's carry</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
@@ -881,20 +873,28 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>[heavy] Bent-over row
+          <t>[heavy] Back squat
+[light] Ring row
+[light] Devil's press
+[light] Biking
+[light] Toes-to-bar</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>[heavy] Deadlift
 [light] Push-up
 [light] Air squat
-[light] Kettlebell swing
-[light] Toes-to-bar</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
+[light] Kipping pull-up
+[light] Running</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
